--- a/Aug_2026/daily Reports/Purchase order Distributor.xlsx
+++ b/Aug_2026/daily Reports/Purchase order Distributor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215CA8D-D09F-4375-BC23-65B9377928E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E43AF58-0C4E-4EF6-919C-FD29BF1F8169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5349,7 +5349,7 @@
       <selection activeCell="E8" sqref="E8"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-      <autoFilter ref="A2:H123" xr:uid="{E4BA5332-0ADE-4A04-8A88-7AA767CAC80D}"/>
+      <autoFilter ref="A2:H123" xr:uid="{241B3344-7395-4E12-A303-098565B5C80A}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="15">
@@ -5417,7 +5417,7 @@
     <col min="2" max="2" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="116" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.1796875" style="20" customWidth="1"/>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L2" s="124">
         <f>SUM(H13:H22)</f>
-        <v>1000</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="L3" s="125">
         <f>SUM(J13:J22)</f>
-        <v>2157410.7000000002</v>
+        <v>8401833.7770000007</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
@@ -5477,7 +5477,7 @@
       <c r="D4" s="169"/>
       <c r="E4" s="158">
         <f ca="1">TODAY()</f>
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="F4" s="159"/>
       <c r="G4" s="160"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="L4" s="125">
         <f>SUM(L13:L19)</f>
-        <v>503389.83050847449</v>
+        <v>1943481.3559322031</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
@@ -5498,7 +5498,7 @@
       <c r="D5" s="169"/>
       <c r="E5" s="158">
         <f ca="1">+E4+1</f>
-        <v>46250</v>
+        <v>46256</v>
       </c>
       <c r="F5" s="159"/>
       <c r="G5" s="160"/>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="L5" s="125">
         <f>L4+L3</f>
-        <v>2660800.5305084744</v>
+        <v>10345315.132932205</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="L6" s="126">
         <f>L5*0.1%</f>
-        <v>2660.8005305084744</v>
+        <v>10345.315132932205</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="23.5" hidden="1" x14ac:dyDescent="0.5">
@@ -5555,7 +5555,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="125">
         <f>+L5+L6</f>
-        <v>2663461.3310389831</v>
+        <v>10355660.448065137</v>
       </c>
       <c r="N8" s="115"/>
     </row>
@@ -5569,7 +5569,7 @@
       <c r="K9" s="1"/>
       <c r="L9" s="130">
         <f>L8*J9</f>
-        <v>1864422.9317272881</v>
+        <v>7248962.3136455957</v>
       </c>
       <c r="N9" s="115"/>
     </row>
@@ -5583,7 +5583,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="130">
         <f>L8*J10</f>
-        <v>799038.3993116949</v>
+        <v>3106698.1344195413</v>
       </c>
       <c r="N10" s="115"/>
     </row>
@@ -5652,17 +5652,17 @@
         <v>1699.7849999999999</v>
       </c>
       <c r="H13" s="103">
-        <v>100</v>
+        <v>399</v>
       </c>
       <c r="I13" s="81"/>
       <c r="J13" s="82">
         <f t="shared" ref="J13:J21" si="0">(H13*G13)</f>
-        <v>169978.5</v>
+        <v>678214.21499999997</v>
       </c>
       <c r="K13" s="91"/>
       <c r="L13" s="88">
         <f>+P13</f>
-        <v>39661.016949152523</v>
+        <v>158247.45762711857</v>
       </c>
       <c r="N13" s="127"/>
       <c r="O13" s="128">
@@ -5671,11 +5671,11 @@
       </c>
       <c r="P13">
         <f>+O13*Q13</f>
-        <v>39661.016949152523</v>
+        <v>158247.45762711857</v>
       </c>
       <c r="Q13">
         <f>+E13*H13</f>
-        <v>4000</v>
+        <v>15960</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.5">
@@ -5704,17 +5704,17 @@
         <v>1699.7849999999999</v>
       </c>
       <c r="H14" s="97">
-        <v>100</v>
+        <v>406</v>
       </c>
       <c r="I14" s="83"/>
       <c r="J14" s="16">
         <f t="shared" si="0"/>
-        <v>169978.5</v>
+        <v>690112.71</v>
       </c>
       <c r="K14" s="92"/>
       <c r="L14" s="89">
         <f>+P14</f>
-        <v>39661.016949152523</v>
+        <v>161023.72881355925</v>
       </c>
       <c r="N14" s="127"/>
       <c r="O14" s="128">
@@ -5723,11 +5723,11 @@
       </c>
       <c r="P14">
         <f>+O14*Q14</f>
-        <v>39661.016949152523</v>
+        <v>161023.72881355925</v>
       </c>
       <c r="Q14">
         <f t="shared" ref="Q14:Q18" si="2">+E14*H14</f>
-        <v>4000</v>
+        <v>16240</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.5">
@@ -5756,17 +5756,17 @@
         <v>1699.7849999999999</v>
       </c>
       <c r="H15" s="97">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I15" s="83"/>
       <c r="J15" s="16">
         <f t="shared" si="0"/>
-        <v>169978.5</v>
+        <v>118984.94999999998</v>
       </c>
       <c r="K15" s="92"/>
       <c r="L15" s="89">
         <f>+P15</f>
-        <v>39661.016949152523</v>
+        <v>27762.711864406767</v>
       </c>
       <c r="N15" s="127"/>
       <c r="O15" s="128">
@@ -5775,11 +5775,11 @@
       </c>
       <c r="P15">
         <f>+O15*Q15</f>
-        <v>39661.016949152523</v>
+        <v>27762.711864406767</v>
       </c>
       <c r="Q15">
         <f t="shared" si="2"/>
-        <v>4000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.5">
@@ -5808,17 +5808,17 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H16" s="97">
-        <v>300</v>
+        <v>797</v>
       </c>
       <c r="I16" s="83"/>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>706060.80000000005</v>
+        <v>1875768.192</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="89">
         <f t="shared" ref="L16:L19" si="3">+P16</f>
-        <v>164745.7627118644</v>
+        <v>437674.57627118647</v>
       </c>
       <c r="N16" s="127"/>
       <c r="O16" s="128">
@@ -5827,11 +5827,11 @@
       </c>
       <c r="P16">
         <f>+O16*Q16</f>
-        <v>164745.7627118644</v>
+        <v>437674.57627118647</v>
       </c>
       <c r="Q16">
         <f t="shared" si="2"/>
-        <v>12000</v>
+        <v>31880</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.5">
@@ -5860,17 +5860,17 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H17" s="97">
-        <v>100</v>
+        <v>662</v>
       </c>
       <c r="I17" s="83"/>
       <c r="J17" s="16">
         <f t="shared" si="0"/>
-        <v>235353.60000000001</v>
+        <v>1558040.8319999999</v>
       </c>
       <c r="K17" s="92"/>
       <c r="L17" s="89">
         <f t="shared" si="3"/>
-        <v>54915.254237288136</v>
+        <v>363538.98305084748</v>
       </c>
       <c r="N17" s="127"/>
       <c r="O17" s="128">
@@ -5879,11 +5879,11 @@
       </c>
       <c r="P17">
         <f>+O17*Q17</f>
-        <v>54915.254237288136</v>
+        <v>363538.98305084748</v>
       </c>
       <c r="Q17">
         <f t="shared" si="2"/>
-        <v>4000</v>
+        <v>26480</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.5">
@@ -5912,17 +5912,17 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H18" s="97">
-        <v>300</v>
+        <v>952</v>
       </c>
       <c r="I18" s="83"/>
       <c r="J18" s="16">
         <f t="shared" si="0"/>
-        <v>706060.80000000005</v>
+        <v>2240566.2719999999</v>
       </c>
       <c r="K18" s="92"/>
       <c r="L18" s="89">
         <f t="shared" si="3"/>
-        <v>164745.7627118644</v>
+        <v>522793.22033898305</v>
       </c>
       <c r="N18" s="127"/>
       <c r="O18" s="128">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="P18">
         <f t="shared" ref="P18" si="4">+O18*Q18</f>
-        <v>164745.7627118644</v>
+        <v>522793.22033898305</v>
       </c>
       <c r="Q18">
         <f t="shared" si="2"/>
-        <v>12000</v>
+        <v>38080</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.5">
@@ -5963,16 +5963,18 @@
         <f>VLOOKUP($B19,'SKU Details'!D12:Y64,17,0)</f>
         <v>1388.742</v>
       </c>
-      <c r="H19" s="97"/>
+      <c r="H19" s="97">
+        <v>893</v>
+      </c>
       <c r="I19" s="9"/>
       <c r="J19" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1240146.6059999999</v>
       </c>
       <c r="K19" s="93"/>
       <c r="L19" s="89">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>272440.67796610156</v>
       </c>
       <c r="N19" s="127"/>
       <c r="O19" s="128">
@@ -5981,11 +5983,11 @@
       </c>
       <c r="P19">
         <f>+O19*Q19</f>
-        <v>0</v>
+        <v>272440.67796610156</v>
       </c>
       <c r="Q19">
         <f>+E19*H19</f>
-        <v>0</v>
+        <v>35720</v>
       </c>
     </row>
     <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.5">
@@ -6164,7 +6166,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Order No " prompt="_x000a_Example,_x000a__x000a_alphabates-Year-Month-order serial No_x000a__x000a_AB-2019-May-01" sqref="E6:H6" xr:uid="{00000000-0002-0000-0100-000000000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Distributor Name " prompt="_x000a_Example,_x000a__x000a_ABC-Distributor" sqref="E3:H3" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Error" error="Please type in the format_x000a__x000a_01-01-2019" prompt="Please type in the format_x000a__x000a_01-01-2019" sqref="E4:H5" xr:uid="{00000000-0002-0000-0100-000002000000}">

--- a/Aug_2026/daily Reports/Purchase order Distributor.xlsx
+++ b/Aug_2026/daily Reports/Purchase order Distributor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E43AF58-0C4E-4EF6-919C-FD29BF1F8169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CFED53-97A8-4E7C-ACFD-024BE7142C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -215,10 +215,10 @@
     <t>Elite Marketing Lahore</t>
   </si>
   <si>
-    <t>4th</t>
+    <t>Ayyan Gujrat</t>
   </si>
   <si>
-    <t>Ayyan Gujrat</t>
+    <t>6th</t>
   </si>
 </sst>
 </file>
@@ -5349,7 +5349,7 @@
       <selection activeCell="E8" sqref="E8"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-      <autoFilter ref="A2:H123" xr:uid="{241B3344-7395-4E12-A303-098565B5C80A}"/>
+      <autoFilter ref="A2:H123" xr:uid="{882532B3-5C28-4013-927A-6A279A5C4E1F}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="15">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L2" s="124">
         <f>SUM(H13:H22)</f>
-        <v>4179</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="L3" s="125">
         <f>SUM(J13:J22)</f>
-        <v>8401833.7770000007</v>
+        <v>2177024.8499999996</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
@@ -5477,7 +5477,7 @@
       <c r="D4" s="169"/>
       <c r="E4" s="158">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46267</v>
       </c>
       <c r="F4" s="159"/>
       <c r="G4" s="160"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="L4" s="125">
         <f>SUM(L13:L19)</f>
-        <v>1943481.3559322031</v>
+        <v>507966.10169491521</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="28.5" x14ac:dyDescent="0.5">
@@ -5498,7 +5498,7 @@
       <c r="D5" s="169"/>
       <c r="E5" s="158">
         <f ca="1">+E4+1</f>
-        <v>46256</v>
+        <v>46268</v>
       </c>
       <c r="F5" s="159"/>
       <c r="G5" s="160"/>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="L5" s="125">
         <f>L4+L3</f>
-        <v>10345315.132932205</v>
+        <v>2684990.9516949151</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="29" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D6" s="171"/>
       <c r="E6" s="162" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="163"/>
       <c r="G6" s="164"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="L6" s="126">
         <f>L5*0.1%</f>
-        <v>10345.315132932205</v>
+        <v>2684.9909516949151</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="23.5" hidden="1" x14ac:dyDescent="0.5">
@@ -5555,7 +5555,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="125">
         <f>+L5+L6</f>
-        <v>10355660.448065137</v>
+        <v>2687675.9426466101</v>
       </c>
       <c r="N8" s="115"/>
     </row>
@@ -5569,7 +5569,7 @@
       <c r="K9" s="1"/>
       <c r="L9" s="130">
         <f>L8*J9</f>
-        <v>7248962.3136455957</v>
+        <v>1881373.159852627</v>
       </c>
       <c r="N9" s="115"/>
     </row>
@@ -5583,7 +5583,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="130">
         <f>L8*J10</f>
-        <v>3106698.1344195413</v>
+        <v>806302.782793983</v>
       </c>
       <c r="N10" s="115"/>
     </row>
@@ -5652,17 +5652,17 @@
         <v>1699.7849999999999</v>
       </c>
       <c r="H13" s="103">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="I13" s="81"/>
       <c r="J13" s="82">
         <f t="shared" ref="J13:J21" si="0">(H13*G13)</f>
-        <v>678214.21499999997</v>
+        <v>254967.74999999997</v>
       </c>
       <c r="K13" s="91"/>
       <c r="L13" s="88">
         <f>+P13</f>
-        <v>158247.45762711857</v>
+        <v>59491.525423728788</v>
       </c>
       <c r="N13" s="127"/>
       <c r="O13" s="128">
@@ -5671,11 +5671,11 @@
       </c>
       <c r="P13">
         <f>+O13*Q13</f>
-        <v>158247.45762711857</v>
+        <v>59491.525423728788</v>
       </c>
       <c r="Q13">
         <f>+E13*H13</f>
-        <v>15960</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.5">
@@ -5704,17 +5704,17 @@
         <v>1699.7849999999999</v>
       </c>
       <c r="H14" s="97">
-        <v>406</v>
+        <v>150</v>
       </c>
       <c r="I14" s="83"/>
       <c r="J14" s="16">
         <f t="shared" si="0"/>
-        <v>690112.71</v>
+        <v>254967.74999999997</v>
       </c>
       <c r="K14" s="92"/>
       <c r="L14" s="89">
         <f>+P14</f>
-        <v>161023.72881355925</v>
+        <v>59491.525423728788</v>
       </c>
       <c r="N14" s="127"/>
       <c r="O14" s="128">
@@ -5723,11 +5723,11 @@
       </c>
       <c r="P14">
         <f>+O14*Q14</f>
-        <v>161023.72881355925</v>
+        <v>59491.525423728788</v>
       </c>
       <c r="Q14">
         <f t="shared" ref="Q14:Q18" si="2">+E14*H14</f>
-        <v>16240</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.5">
@@ -5756,17 +5756,17 @@
         <v>1699.7849999999999</v>
       </c>
       <c r="H15" s="97">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="I15" s="83"/>
       <c r="J15" s="16">
         <f t="shared" si="0"/>
-        <v>118984.94999999998</v>
+        <v>254967.74999999997</v>
       </c>
       <c r="K15" s="92"/>
       <c r="L15" s="89">
         <f>+P15</f>
-        <v>27762.711864406767</v>
+        <v>59491.525423728788</v>
       </c>
       <c r="N15" s="127"/>
       <c r="O15" s="128">
@@ -5775,11 +5775,11 @@
       </c>
       <c r="P15">
         <f>+O15*Q15</f>
-        <v>27762.711864406767</v>
+        <v>59491.525423728788</v>
       </c>
       <c r="Q15">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.5">
@@ -5808,17 +5808,17 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H16" s="97">
-        <v>797</v>
+        <v>150</v>
       </c>
       <c r="I16" s="83"/>
       <c r="J16" s="16">
         <f t="shared" si="0"/>
-        <v>1875768.192</v>
+        <v>353030.40000000002</v>
       </c>
       <c r="K16" s="92"/>
       <c r="L16" s="89">
         <f t="shared" ref="L16:L19" si="3">+P16</f>
-        <v>437674.57627118647</v>
+        <v>82372.881355932201</v>
       </c>
       <c r="N16" s="127"/>
       <c r="O16" s="128">
@@ -5827,11 +5827,11 @@
       </c>
       <c r="P16">
         <f>+O16*Q16</f>
-        <v>437674.57627118647</v>
+        <v>82372.881355932201</v>
       </c>
       <c r="Q16">
         <f t="shared" si="2"/>
-        <v>31880</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.5">
@@ -5860,17 +5860,17 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H17" s="97">
-        <v>662</v>
+        <v>150</v>
       </c>
       <c r="I17" s="83"/>
       <c r="J17" s="16">
         <f t="shared" si="0"/>
-        <v>1558040.8319999999</v>
+        <v>353030.40000000002</v>
       </c>
       <c r="K17" s="92"/>
       <c r="L17" s="89">
         <f t="shared" si="3"/>
-        <v>363538.98305084748</v>
+        <v>82372.881355932201</v>
       </c>
       <c r="N17" s="127"/>
       <c r="O17" s="128">
@@ -5879,11 +5879,11 @@
       </c>
       <c r="P17">
         <f>+O17*Q17</f>
-        <v>363538.98305084748</v>
+        <v>82372.881355932201</v>
       </c>
       <c r="Q17">
         <f t="shared" si="2"/>
-        <v>26480</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.5">
@@ -5912,17 +5912,17 @@
         <v>2353.5360000000001</v>
       </c>
       <c r="H18" s="97">
-        <v>952</v>
+        <v>300</v>
       </c>
       <c r="I18" s="83"/>
       <c r="J18" s="16">
         <f t="shared" si="0"/>
-        <v>2240566.2719999999</v>
+        <v>706060.80000000005</v>
       </c>
       <c r="K18" s="92"/>
       <c r="L18" s="89">
         <f t="shared" si="3"/>
-        <v>522793.22033898305</v>
+        <v>164745.7627118644</v>
       </c>
       <c r="N18" s="127"/>
       <c r="O18" s="128">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="P18">
         <f t="shared" ref="P18" si="4">+O18*Q18</f>
-        <v>522793.22033898305</v>
+        <v>164745.7627118644</v>
       </c>
       <c r="Q18">
         <f t="shared" si="2"/>
-        <v>38080</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.5">
@@ -5963,18 +5963,16 @@
         <f>VLOOKUP($B19,'SKU Details'!D12:Y64,17,0)</f>
         <v>1388.742</v>
       </c>
-      <c r="H19" s="97">
-        <v>893</v>
-      </c>
+      <c r="H19" s="97"/>
       <c r="I19" s="9"/>
       <c r="J19" s="16">
         <f t="shared" si="0"/>
-        <v>1240146.6059999999</v>
+        <v>0</v>
       </c>
       <c r="K19" s="93"/>
       <c r="L19" s="89">
         <f t="shared" si="3"/>
-        <v>272440.67796610156</v>
+        <v>0</v>
       </c>
       <c r="N19" s="127"/>
       <c r="O19" s="128">
@@ -5983,11 +5981,11 @@
       </c>
       <c r="P19">
         <f>+O19*Q19</f>
-        <v>272440.67796610156</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <f>+E19*H19</f>
-        <v>35720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.5">
@@ -6166,7 +6164,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Order No " prompt="_x000a_Example,_x000a__x000a_alphabates-Year-Month-order serial No_x000a__x000a_AB-2019-May-01" sqref="E6:H6" xr:uid="{00000000-0002-0000-0100-000000000000}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Distributor Name " prompt="_x000a_Example,_x000a__x000a_ABC-Distributor" sqref="E3:H3" xr:uid="{00000000-0002-0000-0100-000001000000}"/>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Error" error="Please type in the format_x000a__x000a_01-01-2019" prompt="Please type in the format_x000a__x000a_01-01-2019" sqref="E4:H5" xr:uid="{00000000-0002-0000-0100-000002000000}">
@@ -6226,7 +6224,7 @@
       </c>
       <c r="D3" s="167"/>
       <c r="E3" s="154" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F3" s="155"/>
       <c r="G3" s="156"/>
